--- a/TESTS/zlit_7_halchynskyi_kamiu.xlsx
+++ b/TESTS/zlit_7_halchynskyi_kamiu.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Константи Ілдефонс Галчинський — польський поет XX ст. відомий своєю ліричною і сатиричною поезією</t>
+          <t>Константи Ілдефонс Галчинський</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -645,6 +655,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Маленький гарнізон (близько 200 осіб) 7 днів тримав оборону проти значно більших сил — символ незламності</t>
+          <t>Маленький гарнізон (близько 200 осіб) 7 днів тримав оборону проти значно більших сил</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -706,7 +726,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Скорботно-героїчна — вшановування пам'яті загиблих захисників що зупинились на шляху переважаючих сил</t>
+          <t>Скорботно-героїчна</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,6 +747,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -748,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Конкретних людей — звичайних солдатів що стали героями обравши захист до кінця</t>
+          <t>Конкретних людей</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -769,6 +794,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Символ національної гідності і незламності — «краще гинути стоячи ніж жити навколішки»</t>
+          <t>Символ національної гідності і незламності</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -832,7 +867,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Французький письменник і філософ лауреат Нобелівської премії — представник екзистенціалізму і абсурдизму</t>
+          <t>Французький письменник і філософ лауреат Нобелівської премії</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,6 +888,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -874,7 +914,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Текст що поєднує художні образи з філософськими роздумами — не має жорсткої межі між лірикою і есеїстикою</t>
+          <t>Текст що поєднує художні образи з філософськими роздумами</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -895,6 +935,11 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Абсурд — невідповідність між людським прагненням до смислу і мовчанням байдужого світу; і спосіб жити всупереч</t>
+          <t>Абсурд</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Скільки днів тривала оборона Вестерплятте у вересні 1939 року?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Один день</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Сім днів — з 1 по 7 вересня 1939</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Місяць</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Три дні</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Скільки приблизно польських захисників боронили Вестерплятте проти значно більших сил?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Кілька тисяч</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Близько 200 осіб — невеликий гарнізон</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Кілька десятків тисяч</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Лише 20 осіб</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Чому оборона Вестерплятте стала символом, а не просто воєнним епізодом?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Бо польська армія перемогла</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Бо маленький гарнізон обрав боротьбу до кінця, незважаючи на явну перевагу ворога, показавши незламність</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Бо Вестерплятте урятувала Варшаву</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Бо там підписали перемир'я</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Яких конкретних людей — не абстрактних «героїв» — оспівує Галчинський у своїй пісні?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Польських генералів</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Звичайних солдатів і підофіцерів — прості імена, прості люди, що стали захисниками</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Польського президента</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Лише командира</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Яка тональність пісні Галчинського: тріумфальна чи скорботно-піднята?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Чисто тріумфальна</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Скорботно-героїчна — сум за загиблими, але і гордість за їхній незламний дух</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Іронічна</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Радісна і легка</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Чому вірш названо «піснею», а не «одою» чи «гімном»?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Це випадкова назва</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>«Пісня» підкреслює народний, доступний характер вшанування — це пам'ять простих людей, а не офіційне звеличення</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вірш справді співають</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Галчинський не знав, як назвати</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Яке почуття/стан, за Камю, переживає людина, що зіткнулась з абсурдом?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Радість і полегшення</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Усвідомлення, що між її прагненням до смислу і мовчанням всесвіту — безодня</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Байдужість</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Страх смерті</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Яку відповідь Камю пропонує людині перед обличчям абсурду?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Прийняти його і здатися</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Бунтувати, жити і творити попри абсурд, а не опускати руки</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Знайти релігійне спасіння</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Ігнорувати це питання</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Що спільного між позицією захисників Вестерплятте і відповіддю Камю на абсурд?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого спільного</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Обидва приклади — це вибір спротиву і дії попри безнадійність ситуації</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вони обидва закінчились поразкою</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вони пропонують капітуляцію</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Що символізує образ «пера» у філософській прозі Камю?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Ручку для письма</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Саме письменство і мислення як форму опору абсурду й пошуку правди</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Птаха</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Природу і красу</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Яка роль художника-митця у поглядах Камю?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Митець — розважальник</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Митець, що чесно говорить правду про абсурд і людську долю, виконує найважливіше завдання</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Митець байдужий до суспільства</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Митець має оспівувати переможців</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Яку особисту позицію займав Камю під час Другої світової, відповідно до своїх ідей?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Утік за кордон</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Брав участь у французькому Опорі — на практиці втілюючи ідею бунту і дії попри безнадійність</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Здався нацистам</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Замовк і не писав</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Чим «поезія у прозі», як у Камю, відрізняється від звичайного есею?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вона не відрізняється нічим</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вона поєднує художні образи, ритм і почуття з філософськими роздумами — між поезією і прозою</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вона пишеться у рядки</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вона завжди коротка</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Чим класична балада як жанр (як у Галчинського) відрізняється від звичайного ліричного вірша?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Балада — ліричний монолог</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Балада має чіткий розповідний сюжет, часто з драматичним чи трагічним кінцем</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Балада написана прозою</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Балада обов'язково смішна</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Чому поезія здатна зберегти пам'ять про конкретних людей краще за сухий документ?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Поезія гірше для пам'яті</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вірш передає почуття, створює живий образ, і тому людина в поезії залишається живою в уяві читачів</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Документи важливіші</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Поезія і документ однакові</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Кого Камю описує в «Міфі про Сізіфа» як образ людини перед обличчям абсурду?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Прометея</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Сізіфа, що вічно котить камінь на гору й бачить, як він скочується назад</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Геракла</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Одіссея</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Яким, на думку Камю, повинен бути Сізіф — щасливим чи нещасним?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нещасним і сумним</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Щасливим — бо він обрав бунт і дію, а не пасивну покору безглуздю</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Байдужим</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Мертвим</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Як ідея «щасливого Сізіфа» перегукується з образом захисників Вестерплятте?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Не перегукується</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Обидва знали, що програють, але свідомо обрали боротьбу, надаючи їй сенс своїм вибором</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вестерплятте перемогла</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Сізіф теж погинув</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Яку функцію виконує література у важкі часи, за поглядами і Галчинського, і Камю?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Розвагу без більшого</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Зберігає пам'ять, дає сенс стражданням і надихає на спротив</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Лише документує факти</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Успокоює і примиряє з поразкою</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Чому поєднання творів польського та французького авторів в одній темі є доречним?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Лише через хронологічну близькість</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Обидва митці переживали добу Другої світової й обидва обрали творчість і спротив як відповідь на жорстокість часу</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вони особисто товаришували</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вони написали однаковий текст</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Яка спільна думка об'єднує пісню Галчинського і прозу Камю?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Капітуляція гідніша за опір</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Людська гідність і вибір дії попри безнадійність роблять людину людиною</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Поразка завжди краща за боротьбу</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Мистецтво не має відношення до реального життя</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>А</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>А</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Яку роль відіграє поезія у важкі часи за Галчинським і Камю?</t>
+          <t>Поезія здатна виконувати суспільну функцію — зберігати пам'ять і надихати на спротив — що і робить Галчинський у своїй пісні.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,21 +2133,19 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Що таке «екзистенціалізм» як літературно-філософська течія?</t>
+          <t>Екзистенціалізм — це філософський напрям, що ставить у центр відповідальність і вибір конкретної людини перед обличчям безсмисленого світу.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>А</t>
@@ -1989,6 +2154,11 @@
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,29 +2170,32 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Яку позицію займає людина у світі за екзистенціальною філософією?</t>
+          <t>За екзистенційною філософією Камю, людина перед абсурдом мусить підкоритись йому і не чинити опору.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Що спільного між «Піснею» Галчинського і текстами Камю для 7 класу?</t>
+          <t>Твори Галчинського і Камю об'єднує тема людської гідності й вибору дії попри безнадійні обставини.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,21 +2244,19 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Яка роль лірики Галчинського у польській культурі?</t>
+          <t>Галчинський у польській культурі відомий переважно як автор гумористичних текстів і ліричних поезій.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>А</t>
@@ -2091,6 +2265,11 @@
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,29 +2281,32 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Чому вірші про героїчний опір важливі для підлітків?</t>
+          <t>Вірші про героїчний опір, як «Пісня про Вестерплятте», нічому не навчають підлітків, бо це стара воєнна тема, не актуальна сьогодні.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,27 +2412,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які ідеї об'єднують твори Галчинського і Камю для 7 класу?</t>
+          <t>Що об'єднує Галчинського і Камю у програмному матеріалі?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Людська гідність перед лицем жорстокого світу</t>
+          <t>Обидва пишуть про людську гідність у критичних обставинах</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Спротив і незламність духу</t>
+          <t>Обидва жили в добу Другої світової</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Розважальна функція поезії</t>
+          <t>Обидва закликали до капітуляції</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Осмислення смерті і пам'яті</t>
+          <t>Обидва обрали спротив і творчість замість пасивності</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2251,6 +2443,11 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2295,6 +2492,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2314,7 +2516,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Бунт — продовжувати жити і творити попри безглуздість; «треба уявити Сізіфа щасливим»</t>
+          <t>Бунт</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2335,6 +2537,11 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Сізіф що котить камінь — кожен день він котить знаючи що той скотиться але продовжує: це і є людське існування</t>
+          <t>Сізіф що котить камінь</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
